--- a/Analysis/outputs/reports/summary_statistics.xlsx
+++ b/Analysis/outputs/reports/summary_statistics.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,49 +422,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>price_vnd</t>
         </is>
@@ -507,7 +495,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>area_m2</t>
         </is>
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>price_per_m2</t>
         </is>
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>sophong</t>
         </is>
@@ -614,19 +602,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>missing_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>missing_ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TieuDe</t>
         </is>
@@ -639,7 +627,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>DienTich</t>
         </is>
@@ -652,7 +640,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>GiaVND</t>
         </is>
@@ -665,7 +653,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ViTri</t>
         </is>
@@ -678,7 +666,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>PhanLoai</t>
         </is>
@@ -691,7 +679,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>SoPhong</t>
         </is>
@@ -718,34 +706,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>standardized_location</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>listing_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>median_price_vnd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>median_area_m2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>median_price_per_m2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Quận 1</t>
         </is>
@@ -764,7 +752,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Quận 3</t>
         </is>
@@ -783,7 +771,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Quận 5</t>
         </is>
@@ -802,7 +790,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Quận 10</t>
         </is>
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Phú Nhuận</t>
         </is>
@@ -840,7 +828,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Quận 8</t>
         </is>
@@ -859,7 +847,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Quận 4</t>
         </is>
@@ -878,7 +866,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Quận 2</t>
         </is>
@@ -897,7 +885,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Tân Bình</t>
         </is>
@@ -916,7 +904,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Bình Thạnh</t>
         </is>
@@ -935,7 +923,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Quận 7</t>
         </is>
@@ -954,7 +942,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Quận 11</t>
         </is>
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Gò Vấp</t>
         </is>
@@ -992,7 +980,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Quận 12</t>
         </is>
@@ -1011,7 +999,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Quận 6</t>
         </is>
@@ -1030,7 +1018,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Quận 9</t>
         </is>
@@ -1049,7 +1037,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Bình Chánh</t>
         </is>
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Thủ Đức</t>
         </is>
@@ -1087,7 +1075,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Tân Phú</t>
         </is>
@@ -1106,7 +1094,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Bình Tân</t>
         </is>
@@ -1125,7 +1113,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Nhà Bè</t>
         </is>
@@ -1144,7 +1132,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Hóc Môn</t>
         </is>
@@ -1163,7 +1151,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Cần Giờ</t>
         </is>
@@ -1182,7 +1170,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Củ Chi</t>
         </is>
@@ -1215,34 +1203,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>property_type_clean</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>listing_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>median_price_vnd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>median_area_m2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>median_price_per_m2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Penthouse</t>
         </is>
@@ -1261,7 +1249,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Shophouse</t>
         </is>
@@ -1280,7 +1268,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Nhà nguyên căn</t>
         </is>
@@ -1299,7 +1287,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Căn hộ 2PN</t>
         </is>
@@ -1318,7 +1306,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Căn hộ chung cư</t>
         </is>
@@ -1337,7 +1325,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Studio</t>
         </is>
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Căn hộ 1PN</t>
         </is>
@@ -1375,7 +1363,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Căn hộ mini</t>
         </is>
@@ -1394,7 +1382,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Duplex</t>
         </is>
@@ -1413,7 +1401,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Phòng trọ</t>
         </is>
@@ -1446,17 +1434,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
@@ -1568,37 +1556,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>market_segment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>listing_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>median_price_vnd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>median_area_m2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>median_price_per_m2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>top_property_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>top_location</t>
         </is>
